--- a/output/ks_ds_test.xlsx
+++ b/output/ks_ds_test.xlsx
@@ -4353,6 +4353,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>外五县瑜伽裤</t>
     </r>
     <r>
@@ -4367,6 +4373,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>总部设在</t>
     </r>
     <r>
@@ -4390,6 +4402,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>90后不结婚在西安，难道</t>
     </r>
     <r>
@@ -4434,7 +4452,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4455,13 +4473,6 @@
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -4926,28 +4937,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4956,118 +4970,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5426,8 +5437,8 @@
   <dimension ref="A1:C1426"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="36.5840707964602" customWidth="1"/>
-    <col min="2" max="2" width="50.9823008849558" customWidth="1"/>
+    <col min="1" max="1" width="62.4601769911504" customWidth="1"/>
+    <col min="2" max="2" width="30.5398230088496" customWidth="1"/>
     <col min="3" max="3" width="52.4424778761062" customWidth="1"/>
   </cols>
   <sheetData>
